--- a/20260804_権限設定_使い方.xlsx
+++ b/20260804_権限設定_使い方.xlsx
@@ -476,6 +476,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -621,7 +622,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>条件39件</t>
+          <t>条件41件</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
